--- a/dataset1.xlsx
+++ b/dataset1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://technip-my.sharepoint.com/personal/rahul_agrawal4_ten_com/Documents/Attachments/FPSO MACI files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47E9BC34-389C-472C-A5E4-B5BCB2BAC878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{47E9BC34-389C-472C-A5E4-B5BCB2BAC878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B4877F-66D6-40AA-8BCC-9A3883735EE6}"/>
   <bookViews>
     <workbookView xWindow="11790" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{11048804-B204-4EF9-A095-07AAA27D4C33}"/>
   </bookViews>
@@ -344,9 +344,6 @@
     <t>OFFPEX  ID</t>
   </si>
   <si>
-    <t>Field</t>
-  </si>
-  <si>
     <t>Country</t>
   </si>
   <si>
@@ -501,6 +498,9 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Platform Name</t>
   </si>
 </sst>
 </file>
@@ -864,13 +864,16 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
-        <right/>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </top>
@@ -908,20 +911,9 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
+        <right/>
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </top>
@@ -1201,6 +1193,14 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1215,25 +1215,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83A4C4F5-FA55-4C73-A4B5-A04EF1A644B2}" name="Table1" displayName="Table1" ref="A1:Z26" totalsRowShown="0" dataDxfId="12" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83A4C4F5-FA55-4C73-A4B5-A04EF1A644B2}" name="Table1" displayName="Table1" ref="A1:Z26" totalsRowShown="0" dataDxfId="27" tableBorderDxfId="26">
   <autoFilter ref="A1:Z26" xr:uid="{83A4C4F5-FA55-4C73-A4B5-A04EF1A644B2}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{A5030ED7-95DB-44FA-A10C-E8E9031125B5}" name="OED ID" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{3EB39DB6-C8D6-4A7C-8383-5ADA54176FC2}" name="OFFPEX  ID" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{E319D250-4B8D-453C-9512-C4458F6F7B99}" name="Field" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{41C3C734-AC53-481E-BDEF-1FACADCBD8D5}" name="Country" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{60D07EAD-7312-450B-9FCB-08B6165BE213}" name="WM Region" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F848EA38-087A-4283-9E34-8365C82A55ED}" name="Label" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{CF1EFB06-4725-4FEB-BF8B-689664A88157}" name="Location" dataDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{E8BD2630-04D9-4352-9159-AE8DEF68ADC7}" name="--- HISTORICAL ---" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{267D3AFE-AD63-43BB-AF44-EEBC9452391F}" name="Old Status" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{EBBCD4BC-5C7D-42B1-A18B-BDA8D8BB6C45}" name="WoodMack FID date" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{A2DB9429-46FE-4BE3-B13A-121BC4DD0158}" name="WM Award date" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{E359348C-33EF-489D-8F2B-E70E6D03A78C}" name="WM estimated Installation date" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{0FE86302-836F-47DE-B548-84B916713134}" name="SAM" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{559D5280-5FE9-4228-8CB8-17C4DE72FEB1}" name="SOM" dataDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{BD5CB6D6-EDFF-4183-89ED-E6BD2B8968A4}" name="--- CURRENT ---" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{F707A588-1FAE-495E-BE78-CF05E768B86F}" name="Facility Status" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{A5030ED7-95DB-44FA-A10C-E8E9031125B5}" name="OED ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{3EB39DB6-C8D6-4A7C-8383-5ADA54176FC2}" name="OFFPEX  ID" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{E319D250-4B8D-453C-9512-C4458F6F7B99}" name="Platform Name" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{41C3C734-AC53-481E-BDEF-1FACADCBD8D5}" name="Country" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{60D07EAD-7312-450B-9FCB-08B6165BE213}" name="WM Region" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{F848EA38-087A-4283-9E34-8365C82A55ED}" name="Label" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{CF1EFB06-4725-4FEB-BF8B-689664A88157}" name="Location" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{E8BD2630-04D9-4352-9159-AE8DEF68ADC7}" name="--- HISTORICAL ---" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{267D3AFE-AD63-43BB-AF44-EEBC9452391F}" name="Old Status" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{EBBCD4BC-5C7D-42B1-A18B-BDA8D8BB6C45}" name="WoodMack FID date" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{A2DB9429-46FE-4BE3-B13A-121BC4DD0158}" name="WM Award date" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{E359348C-33EF-489D-8F2B-E70E6D03A78C}" name="WM estimated Installation date" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{0FE86302-836F-47DE-B548-84B916713134}" name="SAM" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{559D5280-5FE9-4228-8CB8-17C4DE72FEB1}" name="SOM" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{BD5CB6D6-EDFF-4183-89ED-E6BD2B8968A4}" name="--- CURRENT ---" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{F707A588-1FAE-495E-BE78-CF05E768B86F}" name="Facility Status" dataDxfId="10"/>
     <tableColumn id="17" xr3:uid="{A642EBD1-6F51-48D1-869A-488F9B932A9D}" name="Operator" dataDxfId="9"/>
     <tableColumn id="18" xr3:uid="{1C948679-BDA0-45ED-A6A9-2098CC16A147}" name="Platform Owner" dataDxfId="8"/>
     <tableColumn id="19" xr3:uid="{739278F5-30D0-4111-8636-13EEF4DB9E8B}" name="Contract Type" dataDxfId="7"/>
@@ -1590,76 +1590,76 @@
         <v>100</v>
       </c>
       <c r="C1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" t="s">
         <v>101</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>102</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>103</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>104</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" t="s">
         <v>105</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="J1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="I1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J1" t="s">
-        <v>107</v>
-      </c>
-      <c r="K1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L1" t="s">
-        <v>109</v>
-      </c>
-      <c r="M1" t="s">
-        <v>110</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>111</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="Q1" t="s">
         <v>143</v>
       </c>
-      <c r="P1" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>144</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>145</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>146</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>147</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>148</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>149</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>150</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>151</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>152</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
@@ -1708,16 +1708,16 @@
         <v>5</v>
       </c>
       <c r="Q2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="R2" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="S2" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="T2" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="T2" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="U2" s="10">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>1800</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
@@ -1778,16 +1778,16 @@
         <v>14</v>
       </c>
       <c r="Q3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="U3" s="2">
         <v>0.12</v>
@@ -1796,7 +1796,7 @@
         <v>211.89</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
@@ -1848,16 +1848,16 @@
         <v>18</v>
       </c>
       <c r="Q4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T4" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="U4" s="2">
         <v>0.1</v>
@@ -1866,7 +1866,7 @@
         <v>211.8</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
@@ -1918,16 +1918,16 @@
         <v>5</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="T5" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U5" s="2">
         <v>0.16</v>
@@ -1936,7 +1936,7 @@
         <v>290</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
@@ -1988,16 +1988,16 @@
         <v>5</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U6" s="2">
         <v>0.15</v>
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
@@ -2058,16 +2058,16 @@
         <v>18</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="U7" s="2">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
@@ -2128,16 +2128,16 @@
         <v>18</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="U8" s="2">
         <v>0</v>
@@ -2146,7 +2146,7 @@
         <v>1100</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
@@ -2198,16 +2198,16 @@
         <v>18</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="U9" s="2">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>1100</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
@@ -2268,16 +2268,16 @@
         <v>14</v>
       </c>
       <c r="Q10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="U10" s="2">
         <v>0.18</v>
@@ -2286,7 +2286,7 @@
         <v>423</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
@@ -2338,16 +2338,16 @@
         <v>18</v>
       </c>
       <c r="Q11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T11" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="U11" s="2">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>500</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
@@ -2408,16 +2408,16 @@
         <v>18</v>
       </c>
       <c r="Q12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T12" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="U12" s="2">
         <v>0.1</v>
@@ -2426,7 +2426,7 @@
         <v>215</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
@@ -2478,16 +2478,16 @@
         <v>18</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U13" s="2">
         <v>0</v>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
@@ -2548,16 +2548,16 @@
         <v>18</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S14" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S14" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="T14" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U14" s="2">
         <v>0.06</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
@@ -2618,16 +2618,16 @@
         <v>18</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S15" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="T15" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U15" s="2">
         <v>0.02</v>
@@ -2636,7 +2636,7 @@
         <v>135</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
@@ -2688,16 +2688,16 @@
         <v>18</v>
       </c>
       <c r="Q16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T16" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="U16" s="2">
         <v>0.14000000000000001</v>
@@ -2706,7 +2706,7 @@
         <v>211.88</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
@@ -2756,16 +2756,16 @@
         <v>18</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U17" s="2">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
@@ -2826,16 +2826,16 @@
         <v>18</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="U18" s="2">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
@@ -2896,16 +2896,16 @@
         <v>18</v>
       </c>
       <c r="Q19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="R19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="R19" s="2" t="s">
+      <c r="S19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="U19" s="2">
         <v>2.5000000000000001E-2</v>
@@ -2914,7 +2914,7 @@
         <v>127</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
@@ -2966,16 +2966,16 @@
         <v>18</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S20" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S20" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="T20" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U20" s="2">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
@@ -3036,16 +3036,16 @@
         <v>18</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S21" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S21" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="T21" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U21" s="2">
         <v>0.05</v>
@@ -3054,7 +3054,7 @@
         <v>400</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
@@ -3106,16 +3106,16 @@
         <v>14</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R22" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S22" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="U22" s="2">
         <v>6.0000000000000001E-3</v>
@@ -3124,7 +3124,7 @@
         <v>300</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
@@ -3176,16 +3176,16 @@
         <v>18</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S23" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S23" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="T23" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U23" s="2">
         <v>0.16</v>
@@ -3194,7 +3194,7 @@
         <v>550</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
@@ -3246,16 +3246,16 @@
         <v>18</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S24" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="T24" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U24" s="2">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
@@ -3316,16 +3316,16 @@
         <v>18</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R25" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S25" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S25" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="T25" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U25" s="2">
         <v>0.22</v>
@@ -3334,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
@@ -3386,16 +3386,16 @@
         <v>18</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S26" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U26" s="8">
         <v>0.22</v>
@@ -3404,7 +3404,7 @@
         <v>400</v>
       </c>
       <c r="W26" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X26" s="8"/>
       <c r="Y26" s="8"/>
